--- a/output/master_performance.xlsx
+++ b/output/master_performance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:W74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,56 +429,122 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>day1_day1</t>
+          <t>Roll No</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>day2_day2</t>
+          <t>Assessment1</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>day3_day3</t>
+          <t>Assessment2</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>day4_day4</t>
+          <t>Assessment3</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>day5_day5</t>
+          <t>Assessment4</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>day6_day6</t>
+          <t>Assessment5</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>day7_day7</t>
+          <t>Assessment6</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Assessment7</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Assessment8</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Assessment9</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Assessment10</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Assessment11</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Assessment12</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Assessment13</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Assessment14</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Assessment15</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Assessment16</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Assessment17</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Assessment18</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Assessment19</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Assessment20</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23lalitthakur@gmail.com</t>
+          <t>akyadav5769@gmail.com</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lalit</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+          <t>Akash Kumar Yadav</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>Absent</t>
@@ -491,7 +557,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>22.00 / 25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -506,14 +572,84 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>18.00 / 20</t>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15.00 / 20</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>akeelkhan3499@gmail.com</t>
+          <t>mohammadakeelbtech23-272liet.in</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,11 +657,7 @@
           <t>Akeel Khan</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>Absent</t>
@@ -543,7 +675,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4.00 / 16</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -552,6 +684,76 @@
         </is>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>7.00 / 15</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -560,19 +762,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>akyadav5769@gmail.com</t>
+          <t>mohammadakeelbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Akash Kumar Yadav</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+          <t>Akeel khan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>Absent</t>
@@ -580,7 +778,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>22.00 / 25</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -600,7 +798,77 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15.00 / 20</t>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>7.00 / 20</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
@@ -615,16 +883,12 @@
           <t>Alok</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
         <is>
           <t>1.00 / 15</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Absent</t>
@@ -646,6 +910,76 @@
         </is>
       </c>
       <c r="I5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -654,27 +988,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>amankumarbtech23-27@liet.in</t>
+          <t>amrendraramtripathibtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aman Kumar</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+          <t>Amrendra Ram Tripathi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.00 / 15</t>
+          <t>14.00 / 15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>14.00 / 15</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -693,6 +1023,76 @@
         </is>
       </c>
       <c r="I6" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -701,84 +1101,146 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>amankumarbtech23-27@liet.in</t>
+          <t>anshtyagi189@gmail.com</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aman kumar</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+          <t>Ansh Tyagi</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>14.00 / 15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>14.00 / 15</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>21.00 / 25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>58.00 / 60</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>13.00 / 16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16.00 / 20</t>
+          <t>10.00 / 10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>amans64788@gmail.com</t>
+          <t>anusingh99361634@gmail.com</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aman Singh</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+          <t>Anurag Kumar Singh</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>15.00 / 15</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20.00 / 25</t>
+          <t>13.00 / 15</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>24.00 / 25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>54.00 / 60</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -787,6 +1249,76 @@
         </is>
       </c>
       <c r="I8" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>12.00 / 15</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>7.00 / 10</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>13.00 / 16</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>13.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -795,45 +1327,111 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>amansingh1btech23-27@liet.in</t>
+          <t>deepanshu3btech23-27@liet.in</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aman Singh</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+          <t>Deepanshu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>15.00 / 15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>14.00 / 15</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>25.00 / 25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>13.00 / 16</t>
+          <t>57.00 / 60</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>9.00 / 10</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -842,45 +1440,111 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>amansingh1btech23-27@liet.in</t>
+          <t>harshitraibtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aman singh</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>13.00 / 15</t>
-        </is>
-      </c>
+          <t>Harshit Rai</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12.00 / 15</t>
+          <t>14.00 / 15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18.00 / 25</t>
+          <t>14.00 / 15</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>47.00 / 60</t>
+          <t>22.00 / 25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>55.00 / 60</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>14.00 / 16</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -889,22 +1553,18 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>amrendraramtripathibtech23-27@liet.in</t>
+          <t>jaisingh1256301@gmail.com</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Amrendra Ram Tripathi</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>14.00 / 15</t>
-        </is>
-      </c>
+          <t>Jai Vardhan Singh</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>14.00 / 15</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -919,15 +1579,85 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>49.00 / 60</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>10.00 / 16</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -936,19 +1666,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ansh.gup067@gmail.com</t>
+          <t>23lalitthakur@gmail.com</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Anshu Gupta</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+          <t>Lalit</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>Absent</t>
@@ -956,17 +1682,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18.00 / 25</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>46.00 / 60</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>15.00 / 16</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -975,6 +1701,76 @@
         </is>
       </c>
       <c r="I12" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>18.00 / 20</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>9.00 / 10</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -983,22 +1779,18 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>anshtyagi189@gmail.com</t>
+          <t>manishjitendramishrabtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ansh Tyagi</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>14.00 / 15</t>
-        </is>
-      </c>
+          <t>Manish Mishra</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>14.00 / 15</t>
+          <t>9.00 / 15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1008,20 +1800,90 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>58.00 / 60</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>13.00 / 16</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>10.00 / 10</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -1030,19 +1892,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>anshtyagi189@gmail.com</t>
+          <t>mdmushroop@gmail.com</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ansh tyagi</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+          <t>Mushroop</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>Absent</t>
@@ -1050,7 +1908,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21.00 / 25</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1069,6 +1927,76 @@
         </is>
       </c>
       <c r="I14" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -1077,27 +2005,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>anushkagargbtech23-27@liet.in</t>
+          <t>nikhilsharmabtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Anushka Garg</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>13.00 / 15</t>
-        </is>
-      </c>
+          <t>Nikhil Sharma</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>12.00 / 15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>23.00 / 25</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1107,7 +2031,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>13.00 / 16</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1117,39 +2041,105 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18.00 / 20</t>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>anusingh99361634@gmail.com</t>
+          <t>nileshsarkar430@email.com</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Anurag Kumar Singh</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+          <t>Nilesh Sarkar</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13.00 / 15</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>24.00 / 25</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>54.00 / 60</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1163,6 +2153,76 @@
         </is>
       </c>
       <c r="I16" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>18.00 / 20</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -1171,37 +2231,33 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ayushpalbtech23-27@liet.in</t>
+          <t>nishaguptabtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ayush Pal</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+          <t>Nisha Gupta</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12.00 / 15</t>
+          <t>13.00 / 15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17.00 / 25</t>
+          <t>9.00 / 15</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>51.00 / 60</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>11.00 / 16</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1210,6 +2266,76 @@
         </is>
       </c>
       <c r="I17" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -1218,66 +2344,128 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ayushsawbtech23-27@liet.in</t>
+          <t>piyushsingh1982004@gmail.com</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ayush Saw</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+          <t>PIYUSH SINGH</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>11.00 / 15</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>18.00 / 25</t>
+          <t>13.00 / 15</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>5.00 / 25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>12.00 / 16</t>
+          <t>44.00 / 60</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
+          <t>14.00 / 16</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>8.00 / 10</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>17.00 / 20</t>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>16.00 / 20</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ayushsingh50593@gmail.com</t>
+          <t>riteshkumar07.com@gmail.com</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ayush Singh</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>14.00 / 15</t>
-        </is>
-      </c>
+          <t>Ritesh Kumar Singh</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>Absent</t>
@@ -1295,36 +2483,102 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>15.00 / 16</t>
+          <t>56.00 / 60</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
+          <t>14.00 / 16</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
           <t>9.00 / 10</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>19.00 / 20</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>chetangoswami2006@gmail.com</t>
+          <t>sanskarbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Chetan Goswami</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+          <t>Sanskar</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>Absent</t>
@@ -1332,72 +2586,208 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>22.00 / 25</t>
+          <t>4.00 / 15</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>59.00 / 60</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>15.00 / 16</t>
+          <t>43.00 / 60</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>9.00 / 10</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>17.00 / 20</t>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>deepanshu3btech23-27@liet.in</t>
+          <t>solankisanskar01@gmail.com</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deepanshu</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+          <t>Sanskar</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>15.00 / 15</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>14.00 / 15</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>25.00 / 25</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>57.00 / 60</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>12.00 / 16</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>12.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -1406,84 +2796,146 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>devashishdobhalbtech23-27@liet.in</t>
+          <t>shivamchaudharybtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Devashish Dobhal</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>12.00 / 15</t>
-        </is>
-      </c>
+          <t>Shivam Chaudhary</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>13.00 / 15</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>16.00 / 25</t>
+          <t>14.00 / 15</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>53.00 / 60</t>
+          <t>20.00 / 25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>10.00 / 16</t>
+          <t>46.00 / 60</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>12.00 / 16</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>12.00 / 20</t>
+          <t>8.00 / 10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>gsinghakca@gmail.com</t>
+          <t>yadavshreyanshi772@gmail.com</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Garima Singh</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+          <t>Shreyanshi Yadav</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>9.00 / 15</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>5.00 / 15</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>49.00 / 60</t>
+          <t>15.00 / 25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>35.00 / 60</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1493,73 +2945,205 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>18.00 / 20</t>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>15.00 / 20</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>gunjanbtech23-27@liet.in</t>
+          <t>sonukumarbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gunjan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+          <t>Sonu Kumar</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>15.00 / 15</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>24.00 / 25</t>
+          <t>15.00 / 15</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>57.00 / 60</t>
+          <t>10.00 / 25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>13.00 / 16</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8.00 / 10</t>
+          <t>2.00 / 16</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>15.00 / 20</t>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2.00 / 20</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>gurmeetsinghbtech23-27@liet.in</t>
+          <t>tarunkumar1btech23-27@liet.in</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gurmeet Singh</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+          <t>Tarun kumar</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>Absent</t>
@@ -1567,25 +3151,95 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>18.00 / 25</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>39.00 / 60</t>
+          <t>21.00 / 25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14.00 / 16</t>
+          <t>52.00 / 60</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>9.00 / 16</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
+        <is>
+          <t>9.00 / 10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>14.00 / 20</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -1594,84 +3248,146 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>happybtech23-27@liet.in</t>
+          <t>vibhubtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Happy</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
+          <t>Vibhu</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>12.00 / 15</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16.00 / 25</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>50.00 / 60</t>
+          <t>24.00 / 25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>11.00 / 16</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8.00 / 10</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>17.00 / 20</t>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>harshitraibtech23-27@liet.in</t>
+          <t>yashbansal216@gmail.com</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Harshit Rai</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>14.00 / 15</t>
-        </is>
-      </c>
+          <t>Yash Bansal</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>14.00 / 15</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>22.00 / 25</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>55.00 / 60</t>
+          <t>11.00 / 25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>14.00 / 16</t>
+          <t>48.00 / 60</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1680,6 +3396,76 @@
         </is>
       </c>
       <c r="I27" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -1688,17 +3474,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>jaisingh1256301@gmail.com</t>
+          <t>amankumarbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jai Vardhan Singh</t>
+          <t>Aman Kumar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>2301530000000</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1708,17 +3494,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>5.00 / 15</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>49.00 / 60</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>10.00 / 16</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1727,6 +3513,76 @@
         </is>
       </c>
       <c r="I28" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>16.00 / 20</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>8.00 / 16</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>8.00 / 16</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>7.00 / 10</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>15.00 / 16</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>15.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>18.00 / 20</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -1735,92 +3591,232 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kanak.gup1234@gmail.com</t>
+          <t>amans64788@gmail.com</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kanak Gupta</t>
+          <t>Aman Singh</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>2301530000000</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>15.00 / 15</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>14.00 / 15</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>25.00 / 25</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>52.00 / 60</t>
+          <t>20.00 / 25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>15.00 / 16</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>12.00 / 16</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>12.00 / 16</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
           <t>9.00 / 10</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>17.00 / 20</t>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ksah9189@gmail.com</t>
+          <t>ayushpalbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Krishna Kumar Sah</t>
+          <t>Ayush Pal</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>2301530000000</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.00 / 15</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>10.00 / 25</t>
+          <t>12.00 / 15</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>17.00 / 25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8.00 / 16</t>
+          <t>51.00 / 60</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>11.00 / 16</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>19.00 / 20</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -1829,64 +3825,134 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kumarritik38269@gmail.com</t>
+          <t>gunjanbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ritik</t>
+          <t>Gunjan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>9.00 / 15</t>
+          <t>2301530000000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>24.00 / 25</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>57.00 / 60</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>13.00 / 16</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>8.00 / 10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>15.00 / 20</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
           <t>15.00 / 15</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>15.00 / 25</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>46.00 / 60</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>10.00 / 16</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2.00 / 10</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>14.00 / 20</t>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>15.00 / 16</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>15.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ky205426@gmail.com</t>
+          <t>gurmeetsinghbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kapil Yadav</t>
+          <t>Gurmeet singh</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>2301530000000</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1896,44 +3962,114 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12.00 / 25</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>54.00 / 60</t>
+          <t>18.00 / 25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>13.00 / 16</t>
+          <t>39.00 / 60</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4.00 / 10</t>
+          <t>14.00 / 16</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>14.00 / 20</t>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>manishjitendramishrabtech23-27@liet.in</t>
+          <t>happybtech23-27@gmail.com</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Manish Mishra</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>9.00 / 15</t>
+          <t>2301530000000</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1962,6 +4098,76 @@
         </is>
       </c>
       <c r="I33" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -1970,17 +4176,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>mohammadakeelbtech23-27@liet.in</t>
+          <t>ky205426@gmail.com</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Akeel khan</t>
+          <t>Kapil Yadav</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>2301530000000</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1995,114 +4201,324 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>12.00 / 25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>54.00 / 60</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>13.00 / 16</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>7.00 / 20</t>
+          <t>4.00 / 10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>14.00 / 20</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>11.00 / 16</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>11.00 / 16</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>12.00 / 15</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>7.00 / 10</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>13.00 / 16</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>13.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>16.00 / 20</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>12.00 / 15</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>mohitbtech23-27@liet.in</t>
+          <t>prateekraibtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MOHIT</t>
+          <t>Prateek Rai</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>10.00 / 15</t>
+          <t>2301530000000</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>12.00 / 15</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>17.00 / 25</t>
+          <t>15.00 / 15</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>57.00 / 60</t>
+          <t>22.00 / 25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>11.00 / 16</t>
+          <t>55.00 / 60</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>13.00 / 16</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>18.00 / 20</t>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>13.00 / 20</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>13.00 / 16</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>13.00 / 16</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>15.00 / 16</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>15.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>mohitkumar746185@gmail.com</t>
+          <t>kumarritik38269@gmail.com</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mohit Kumar</t>
+          <t>RITIK</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>2301530000000</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>9.00 / 15</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>15.00 / 15</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>15.00 / 25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>46.00 / 60</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>9.00 / 10</t>
+          <t>10.00 / 16</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
+        <is>
+          <t>2.00 / 10</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>14.00 / 20</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>12.00 / 16</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>12.00 / 16</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>10.00 / 15</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>5.00 / 10</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>16.00 / 20</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>11.00 / 15</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -2111,64 +4527,134 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>mushroopbtech23-27@liet.in</t>
+          <t>rahulyadavbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mushroop</t>
+          <t>Rahul Yadav</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>2301530000000</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>12.00 / 15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>17.00 / 25</t>
+          <t>9.00 / 15</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>49.00 / 60</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
+          <t>55.00 / 60</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
           <t>12.00 / 16</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>7.00 / 10</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>15.00 / 20</t>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>14.00 / 16</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>14.00 / 16</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>nikhilsharmabtech23-27@liet.in</t>
+          <t>kuma</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nikhil Sharma</t>
+          <t>Ritik</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>12.00 / 15</t>
+          <t>2301530000000</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2197,6 +4683,76 @@
         </is>
       </c>
       <c r="I38" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>13.00 / 20</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>3.00 / 15</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -2205,92 +4761,232 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>nileshsarkar430@email.com</t>
+          <t>satyanshrawatbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nilesh Sarkar</t>
+          <t>Satyansh Rawat</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>2301530000000</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>11.00 / 15</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>13.00 / 15</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>15.00 / 25</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>53.00 / 60</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>10.00 / 16</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>18.00 / 20</t>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>11.00 / 15</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>12.00 / 15</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>nileshsarkar430@gmail.com</t>
+          <t>sonukumar3570357@gmail.com</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nilesh Sarkar</t>
+          <t>Sonu Kumar</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>2301530000000</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>7.00 / 20</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>6.00 / 20</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>5.00 / 15</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
           <t>15.00 / 15</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>14.00 / 15</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>16.00 / 25</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>42.00 / 60</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>13.00 / 16</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>10.00 / 10</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -2299,22 +4995,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>nishaguptabtech23-27@liet.in</t>
+          <t>sringanisinghbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nisha Gupta</t>
+          <t>Sringani Singh</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>13.00 / 15</t>
+          <t>2301530000000</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>9.00 / 15</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2324,12 +5020,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>14.00 / 25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>49.00 / 60</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2338,6 +5034,76 @@
         </is>
       </c>
       <c r="I41" t="inlineStr">
+        <is>
+          <t>10.00 / 10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>14.00 / 20</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>13.00 / 16</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>13.00 / 16</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>9.00 / 10</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>18.00 / 20</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
@@ -2346,252 +5112,602 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>piyushsingh1982004@gmail.com</t>
+          <t>chetangoswami2006@gmail.com</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PIYUSH SINGH</t>
+          <t>chetan goswami</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>2301530000000</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>13.00 / 15</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>5.00 / 25</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>44.00 / 60</t>
+          <t>22.00 / 25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>59.00 / 60</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>15.00 / 16</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>9.00 / 10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>17.00 / 20</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t>14.00 / 16</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>8.00 / 10</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>16.00 / 20</t>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>14.00 / 16</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>prateekraibtech23-27@liet.in</t>
+          <t>amansingh1btech23-27@liet.in</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Prateek Rai</t>
+          <t>Aman singh</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>2301530100020</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>13.00 / 15</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>12.00 / 15</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>18.00 / 25</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>47.00 / 60</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>13.00 / 16</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>9.00 / 10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>12.00 / 16</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>12.00 / 16</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
           <t>15.00 / 15</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>22.00 / 25</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>55.00 / 60</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>13.00 / 16</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>13.00 / 20</t>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>12.00 / 15</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>12.00 / 15</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>premkumarjhabtech23-27@liet.in</t>
+          <t>ansh.gup067@gmail.com</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Prem Kumar Jha</t>
+          <t>Anshu Gupta</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>2301530100029</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>14.00 / 15</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>23.00 / 25</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>53.00 / 60</t>
+          <t>18.00 / 25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>14.00 / 16</t>
+          <t>46.00 / 60</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>15.00 / 16</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>Absent</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>12.00 / 15</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>15.00 / 16</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>15.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>17.00 / 20</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>11.00 / 15</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>8.00 / 15</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>pushpendrayadav8434@gmail.com</t>
+          <t>ksah9189@gmail.com</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pushpendra Yadav</t>
+          <t>Krishna Kumar sah</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>2301530100072</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>11.00 / 15</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>13.00 / 25</t>
+          <t>8.00 / 15</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>52.00 / 60</t>
+          <t>10.00 / 25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>5.00 / 16</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>3.00 / 10</t>
+          <t>8.00 / 16</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>Absent</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1.00 / 10</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>3.00 / 16</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>3.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>10.00 / 20</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>rahulyadavbtech23-27@liet.in</t>
+          <t>premkumarjhabtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Rahul Yadav</t>
+          <t>Prem Kumar Jha</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>2301530100104</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>23.00 / 25</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>53.00 / 60</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>14.00 / 16</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>14.00 / 16</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>14.00 / 16</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>16.00 / 20</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
           <t>12.00 / 15</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>9.00 / 15</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>55.00 / 60</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>12.00 / 16</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Absent</t>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>12.00 / 15</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>riteshkumar07.com@gmail.com</t>
+          <t>vk9491015@gmail.com</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ritesh Kumar Singh</t>
+          <t>Vishal kumar</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>2301530100155</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2601,44 +5717,114 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>12.00 / 15</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>56.00 / 60</t>
+          <t>17.00 / 25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>14.00 / 16</t>
+          <t>47.00 / 60</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>8.00 / 16</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>Absent</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>8.00 / 20</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>7.00 / 15</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>16.00 / 20</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>19.00 / 20</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>7.00 / 15</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>8.00 / 15</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>8.00 / 15</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>rohitkumarbtech23-27@liet.in</t>
+          <t>kanak</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Rohit Kumar</t>
+          <t>Kanak Gupta</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>2301531530030</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2648,237 +5834,587 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>16.00 / 25</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>36.00 / 60</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>6.00 / 16</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6.00 / 10</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10.00 / 20</t>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>sakshichauhanbtech23-27@liet.in</t>
+          <t>kanak.gup1234@gmail.com</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sakshi Chauhan</t>
+          <t>Kanak Gupta</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>2301531530030</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>14.00 / 15</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>14.00 / 15</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>15.00 / 25</t>
-        </is>
-      </c>
       <c r="F49" t="inlineStr">
         <is>
+          <t>25.00 / 25</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
           <t>52.00 / 60</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>15.00 / 16</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>10.00 / 10</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>15.00 / 20</t>
+          <t>9.00 / 10</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>17.00 / 20</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>14.00 / 16</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>14.00 / 16</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>9.00 / 10</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>sanskarbtech23-27@liet.in</t>
+          <t>vishujeetrathor@gmail.com</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sanskar</t>
+          <t>Vishujeet</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>2301531530054</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>4.00 / 15</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>11.00 / 15</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>43.00 / 60</t>
+          <t>11.00 / 25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>47.00 / 60</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>10.00 / 16</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>9.00 / 10</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>19.00 / 20</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>15.00 / 16</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>15.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>10.00 / 15</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>satyanshrawatbtech23-27@liet.in</t>
+          <t>ayushsingh50593@gmail.com</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Satyansh Rawat</t>
+          <t>Ayush singh</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>11.00 / 15</t>
+          <t>2301531540009</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>15.00 / 16</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>9.00 / 10</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>19.00 / 20</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>14.00 / 16</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>14.00 / 16</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>12.00 / 15</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>9.00 / 10</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>17.00 / 20</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
           <t>13.00 / 15</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>15.00 / 25</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>53.00 / 60</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>10.00 / 16</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Absent</t>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>shivamchaudharybtech23-27@liet.in</t>
+          <t>happybtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Shivam Chaudhary</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>2301531540016</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>12.00 / 15</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>16.00 / 25</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>50.00 / 60</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>11.00 / 16</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>8.00 / 10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>17.00 / 20</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>12.00 / 16</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>12.00 / 16</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>9.00 / 16</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>9.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>19.00 / 20</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
           <t>14.00 / 15</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>20.00 / 25</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>46.00 / 60</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>12.00 / 16</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>8.00 / 10</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Absent</t>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>shivangipandeyabc@gmail.com</t>
+          <t>mushroopbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Shivangi Pandey</t>
+          <t>Mushroop</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>15.00 / 15</t>
+          <t>2301531540024</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>15.00 / 15</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2888,86 +6424,226 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>57.00 / 60</t>
+          <t>17.00 / 25</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>15.00 / 16</t>
+          <t>49.00 / 60</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
+          <t>12.00 / 16</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>7.00 / 10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>15.00 / 20</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
           <t>9.00 / 10</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>19.00 / 20</t>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>14.00 / 16</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>14.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>16.00 / 20</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>14.00 / 20</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>12.00 / 15</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>12.00 / 15</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>12.00 / 15</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>sonukumarbtech23-27@liet.in</t>
+          <t>nileshsarkar430@gmail.com</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sonu Kumar</t>
+          <t>Nilesh sarkar</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>2301531540030</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>15.00 / 15</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>16.00 / 25</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>42.00 / 60</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>13.00 / 16</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10.00 / 10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>13.00 / 16</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>13.00 / 16</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t>15.00 / 15</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>10.00 / 25</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>2.00 / 16</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2.00 / 20</t>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>sringanisinghbtech23-27@liet.in</t>
+          <t>piyushsinghbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sringani Singh</t>
+          <t>PIYUSH SINGH</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>2301531540031</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2977,12 +6653,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>14.00 / 25</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>49.00 / 60</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2992,170 +6668,450 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>10.00 / 10</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>14.00 / 20</t>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>14.00 / 16</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>14.00 / 16</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>9.00 / 10</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>19.00 / 20</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>tarunkumar1btech23-27@liet.in</t>
+          <t>sakshichauhanbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tarun kumar</t>
+          <t>Sakshi Chauhan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>2301531540037</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>14.00 / 15</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>21.00 / 25</t>
+          <t>14.00 / 15</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
+          <t>15.00 / 25</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
           <t>52.00 / 60</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>9.00 / 16</t>
-        </is>
-      </c>
       <c r="H56" t="inlineStr">
         <is>
+          <t>15.00 / 16</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10.00 / 10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>15.00 / 20</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>14.00 / 16</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>14.00 / 16</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
           <t>9.00 / 10</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>14.00 / 20</t>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>18.00 / 20</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>19.00 / 20</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>vaibhavmishrabtech23-27@liet.in</t>
+          <t>vineet333roy@gmail.com</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Vaibhav Mishra</t>
+          <t>Vineet Kumar Roy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>2301531540045</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>7.00 / 10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>17.00 / 20</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>18.00 / 20</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>11.00 / 15</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
           <t>13.00 / 15</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>15.00 / 25</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>5.00 / 10</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Absent</t>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>vibhubtech23-27@liet.in</t>
+          <t>vivekyadavbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Vibhu</t>
+          <t>Vivek yadav</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>2301531540048</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>14.00 / 15</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>24.00 / 25</t>
+          <t>13.00 / 15</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>17.00 / 25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>50.00 / 60</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>11.00 / 16</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>6.00 / 10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>13.00 / 20</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>14.00 / 16</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>14.00 / 16</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>12.00 / 15</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>10.00 / 10</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>6.00 / 16</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>6.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>vineet333roy@gmail.com</t>
+          <t>akeelkhan3499@gmail.com</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Vineet Kumar Roy</t>
+          <t>Akeel khan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>2301720000000</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3180,190 +7136,470 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>7.00 / 10</t>
+          <t>4.00 / 16</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>17.00 / 20</t>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>vipulpandeybtech23-27@liet.in</t>
+          <t>anushkagargbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Vipul Pandey</t>
+          <t>Anushka garg</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>2301720000000</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t>13.00 / 15</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>23.00 / 25</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>13.00 / 16</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>18.00 / 20</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>14.00 / 16</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>14.00 / 16</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
           <t>15.00 / 15</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>22.00 / 25</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>54.00 / 60</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>11.00 / 16</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>9.00 / 10</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>18.00 / 20</t>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>19.00 / 20</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>vishujeetrathor@gmail.com</t>
+          <t>devashishdobhalbtech23-27@gmail.com</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Vishujeet Rathore</t>
+          <t>Devashish Dobhal</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>2301721530007</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>11.00 / 15</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>11.00 / 25</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>47.00 / 60</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>10.00 / 16</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>9.00 / 10</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>19.00 / 20</t>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>16.00 / 20</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>vivekyadavbtech23-27@liet.in</t>
+          <t>devashishdobhalbtech23-27@liet.in</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Vivek Yadav</t>
+          <t>Devashish Dobhal</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>14.00 / 15</t>
+          <t>2301721530007</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>12.00 / 15</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>13.00 / 15</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>17.00 / 25</t>
-        </is>
-      </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>50.00 / 60</t>
+          <t>16.00 / 25</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>11.00 / 16</t>
+          <t>53.00 / 60</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6.00 / 10</t>
+          <t>10.00 / 16</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>13.00 / 20</t>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>12.00 / 20</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>10.00 / 16</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>10.00 / 16</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>12.00 / 15</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>7.00 / 10</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>12.00 / 16</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>12.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>15.00 / 20</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>6.00 / 15</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>8.00 / 15</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>8.00 / 15</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>vk9491015@gmail.com</t>
+          <t>gsinghakca@gmail.com</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Vishal Kumar</t>
+          <t>Garima singh</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>2301721530008</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>12.00 / 15</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>17.00 / 25</t>
+          <t>9.00 / 15</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>47.00 / 60</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>8.00 / 16</t>
+          <t>49.00 / 60</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3373,39 +7609,109 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>8.00 / 20</t>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>18.00 / 20</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>13.00 / 16</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>13.00 / 16</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>12.00 / 16</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>12.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Absent</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>yadavshreyanshi772@gmail.com</t>
+          <t>tarunpandit885@gmail.com</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Shreyanshi Yadav</t>
+          <t>Tarun kumar</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>2301721530024</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>5.00 / 15</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>15.00 / 25</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>35.00 / 60</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3420,24 +7726,94 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>15.00 / 20</t>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>12.00 / 16</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>12.00 / 16</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>yashbansal216@gmail.com</t>
+          <t>manishmishra9067@gmail.com</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Yash Bansal</t>
+          <t>Manish jitendra mishra</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Absent</t>
+          <t>2401530000000</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3447,12 +7823,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>11.00 / 25</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>48.00 / 60</t>
+          <t>Absent</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3468,6 +7844,1129 @@
       <c r="I65" t="inlineStr">
         <is>
           <t>Absent</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>5.00 / 16</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>5.00 / 16</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ayushsawbtech23-27@liet.in</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Ayush Saw</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2401530109008</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>11.00 / 15</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>18.00 / 25</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>12.00 / 16</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>8.00 / 10</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>17.00 / 20</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>13.00 / 16</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>13.00 / 16</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>9.00 / 10</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>15.00 / 16</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>15.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>18.00 / 20</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>18.00 / 20</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>vipulpandeybtech23-27@liet.in</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>VIPUL PANDEY</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2401530109021</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>22.00 / 25</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>54.00 / 60</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>11.00 / 16</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>9.00 / 10</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>18.00 / 20</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>13.00 / 16</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>13.00 / 16</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>7.00 / 10</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>18.00 / 20</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>19.00 / 20</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>akyadav5769@gmail</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Akash kumar yadav</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2401720000000</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>12.00 / 16</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>12.00 / 16</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>mohitkumar746185@gmail.com</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Mohit kumar</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2401720000000</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>9.00 / 10</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>13.00 / 16</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>13.00 / 16</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>pushpendrayadav8434@gmail.com</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Pushpendra yadav</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2401720000000</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>11.00 / 15</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>13.00 / 25</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>52.00 / 60</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>5.00 / 16</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3.00 / 10</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>12.00 / 16</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>12.00 / 16</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>rohitkumarbtech23-27@liet.in</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Rohit Kumar</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2401720000000</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>16.00 / 25</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>36.00 / 60</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>6.00 / 16</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>6.00 / 10</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>10.00 / 20</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>11.00 / 15</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>6.00 / 10</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>9.00 / 16</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>9.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>13.00 / 20</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>9.00 / 15</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>shivangipandeyabc@gmail.com</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Shivangi Pandey</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2401720109026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>57.00 / 60</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>15.00 / 16</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>9.00 / 10</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>19.00 / 20</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>14.00 / 16</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>14.00 / 16</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>9.00 / 10</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>15.00 / 15</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>14.00 / 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>vaibhavmishrabtech23-27@liet.in</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Vaibhav Mishra</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2401721539008</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>15.00 / 25</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>5.00 / 10</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>6.00 / 10</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>16.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>20.00 / 20</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>mohitbtech23-27@liet.in</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>MOHIT</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>241721539004</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>10.00 / 15</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>12.00 / 15</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>17.00 / 25</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>57.00 / 60</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>11.00 / 16</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>18.00 / 20</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>9.00 / 10</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>11.00 / 16</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>11.00 / 16</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>18.00 / 20</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>11.00 / 15</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>6.00 / 15</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>11.00 / 15</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>13.00 / 15</t>
         </is>
       </c>
     </row>
